--- a/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,15</t>
+          <t>0,43; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,73</t>
+          <t>0,35; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,44</t>
+          <t>0,32; 2,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,48</t>
+          <t>0,33; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,81</t>
+          <t>0,7; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,41</t>
+          <t>0,52; 3,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,52</t>
+          <t>1,09; 4,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,88</t>
+          <t>0,65; 2,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,18</t>
+          <t>1,16; 4,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,65</t>
+          <t>1,1; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,66</t>
+          <t>0,85; 2,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,2</t>
+          <t>1,11; 3,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,07</t>
+          <t>0,42; 3,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,79</t>
+          <t>2,03; 9,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,14</t>
+          <t>0,41; 3,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,28</t>
+          <t>0,6; 5,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,5</t>
+          <t>0,39; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,14</t>
+          <t>0,66; 3,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,67</t>
+          <t>1,85; 6,04</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,06</t>
+          <t>0,0; 16,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,62</t>
+          <t>2,94; 14,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,91</t>
+          <t>1,98; 9,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,75</t>
+          <t>1,0; 8,77</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,23</t>
+          <t>0,0; 43,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,91</t>
+          <t>0,0; 29,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,6</t>
+          <t>0,0; 22,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 24,72</t>
+          <t>2,81; 29,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 12,74</t>
+          <t>1,7; 13,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,52</t>
+          <t>1,39; 12,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 20,25</t>
+          <t>3,44; 19,6</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,14</t>
+          <t>0,0; 31,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,69</t>
+          <t>0,0; 32,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,82</t>
+          <t>0,0; 35,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,32</t>
+          <t>0,0; 17,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 27,11</t>
+          <t>5,09; 27,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 24,42</t>
+          <t>2,74; 23,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 14,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 22,89</t>
+          <t>5,24; 23,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 19,24</t>
+          <t>2,76; 20,48</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,23</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,8</t>
+          <t>0,97; 2,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,69</t>
+          <t>1,39; 3,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>1,04; 2,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,78</t>
+          <t>1,26; 2,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,03</t>
+          <t>1,3; 3,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,16; 2,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,47</t>
+          <t>1,31; 2,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,94</t>
+          <t>1,61; 2,98</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10218</t>
+          <t>0; 8637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>933; 6747</t>
+          <t>920; 7489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7517</t>
+          <t>0; 7063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12353</t>
+          <t>0; 12572</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1637; 12802</t>
+          <t>1650; 12081</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1918; 14742</t>
+          <t>1916; 14698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6136</t>
+          <t>0; 5120</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1688; 12127</t>
+          <t>884; 11327</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2787; 15805</t>
+          <t>2905; 16918</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1051; 10646</t>
+          <t>1632; 11468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4317; 17740</t>
+          <t>4287; 18382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2997; 16560</t>
+          <t>3733; 17076</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4699; 17032</t>
+          <t>4713; 16738</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7777; 24193</t>
+          <t>7274; 23948</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8448; 26326</t>
+          <t>8420; 27000</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7243; 22992</t>
+          <t>7954; 23877</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4517</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>956; 9300</t>
+          <t>951; 8418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3165; 13787</t>
+          <t>3189; 14240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 9466</t>
+          <t>0; 8737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1092; 10821</t>
+          <t>1064; 9750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1085; 9622</t>
+          <t>1085; 10761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>900; 10412</t>
+          <t>902; 11252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3215; 15381</t>
+          <t>3252; 15352</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5388; 19215</t>
+          <t>6278; 20492</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2042</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7671</t>
+          <t>0; 6764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 5721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2499; 13688</t>
+          <t>2954; 14400</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>0; 4720</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6494</t>
+          <t>0; 5887</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2960; 13338</t>
+          <t>2959; 14252</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>934; 8492</t>
+          <t>968; 8511</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5985</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6669</t>
+          <t>0; 6464</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 4772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5220</t>
+          <t>0; 5244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1076; 9010</t>
+          <t>1025; 10632</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1033; 7788</t>
+          <t>1037; 8304</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>954; 8012</t>
+          <t>969; 8412</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2054; 11686</t>
+          <t>1983; 11310</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 5084</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 4810</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4460</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5675</t>
+          <t>0; 4566</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2178; 11176</t>
+          <t>2101; 11252</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1257; 10962</t>
+          <t>1230; 10326</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6558</t>
+          <t>0; 6173</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2267; 12862</t>
+          <t>2942; 13399</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2002; 11032</t>
+          <t>1582; 11743</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5288; 20210</t>
+          <t>5347; 19648</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9777; 27556</t>
+          <t>9537; 27679</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10375; 27925</t>
+          <t>10492; 28417</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9755; 28288</t>
+          <t>10421; 28616</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18523; 42096</t>
+          <t>19166; 41051</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14305; 33665</t>
+          <t>14456; 34645</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17969; 41980</t>
+          <t>18906; 41571</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33115; 61772</t>
+          <t>32835; 61688</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29124; 54874</t>
+          <t>30033; 55725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,5</t>
+          <t>0,43; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,57</t>
+          <t>0,26; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,19</t>
+          <t>0,33; 4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,08</t>
+          <t>0,69; 4,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,68</t>
+          <t>0,33; 4,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,69</t>
+          <t>1,1; 4,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,97</t>
+          <t>0,51; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,11</t>
+          <t>1,07; 3,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,61</t>
+          <t>1,05; 3,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,73</t>
+          <t>0,88; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,32</t>
+          <t>1,0; 3,15</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,68</t>
+          <t>0,42; 3,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,08</t>
+          <t>1,99; 9,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 8,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,73</t>
+          <t>0,41; 4,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,9</t>
+          <t>0,6; 5,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,87</t>
+          <t>0,39; 4,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,13</t>
+          <t>0,63; 2,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,04</t>
+          <t>1,6; 5,68</t>
         </is>
       </c>
     </row>
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,81</t>
+          <t>0,0; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 14,32</t>
+          <t>2,9; 13,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 8,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,52</t>
+          <t>1,96; 9,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,77</t>
+          <t>0,99; 9,5</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,35</t>
+          <t>0,0; 42,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,0</t>
+          <t>0,0; 33,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,46</t>
+          <t>0,0; 18,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 11,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 29,17</t>
+          <t>2,88; 26,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,59</t>
+          <t>1,69; 13,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,09</t>
+          <t>1,38; 11,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 19,6</t>
+          <t>3,4; 18,03</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,39</t>
+          <t>0,0; 24,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,18</t>
+          <t>0,0; 29,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,4</t>
+          <t>0,0; 41,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,95</t>
+          <t>0,0; 22,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 27,29</t>
+          <t>5,14; 26,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 23,0</t>
+          <t>2,73; 22,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,83</t>
+          <t>0,0; 14,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 23,85</t>
+          <t>5,5; 23,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 20,48</t>
+          <t>3,55; 20,55</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,14</t>
+          <t>0,92; 3,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>0,99; 2,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,76</t>
+          <t>1,52; 3,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,85</t>
+          <t>0,99; 2,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,71</t>
+          <t>1,25; 2,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,12</t>
+          <t>1,25; 3,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,55</t>
+          <t>1,19; 2,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,47</t>
+          <t>1,29; 2,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,98</t>
+          <t>1,55; 2,92</t>
         </is>
       </c>
     </row>
@@ -1913,27 +1913,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8637</t>
+          <t>0; 9486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>920; 7489</t>
+          <t>930; 8067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 5128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7063</t>
+          <t>0; 7371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12572</t>
+          <t>0; 12437</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1650; 12081</t>
+          <t>1210; 12096</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1916; 14698</t>
+          <t>1906; 14678</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 5353</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>884; 11327</t>
+          <t>892; 12601</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2905; 16918</t>
+          <t>2857; 16623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1632; 11468</t>
+          <t>1043; 12619</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4287; 18382</t>
+          <t>4322; 17415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3733; 17076</t>
+          <t>2951; 16359</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4713; 16738</t>
+          <t>4373; 16225</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7274; 23948</t>
+          <t>6984; 22589</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8420; 27000</t>
+          <t>8688; 28293</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7954; 23877</t>
+          <t>7173; 22634</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 4577</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>951; 8418</t>
+          <t>963; 8520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3189; 14240</t>
+          <t>3114; 14744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8737</t>
+          <t>0; 10060</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1064; 9750</t>
+          <t>1068; 10823</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1085; 10761</t>
+          <t>1087; 9826</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>902; 11252</t>
+          <t>898; 9274</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3252; 15352</t>
+          <t>3072; 13974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6278; 20492</t>
+          <t>5435; 19276</t>
         </is>
       </c>
     </row>
@@ -2412,37 +2412,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6764</t>
+          <t>0; 6779</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5721</t>
+          <t>0; 7241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2954; 14400</t>
+          <t>2917; 13851</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4720</t>
+          <t>0; 5025</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5887</t>
+          <t>0; 7532</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2959; 14252</t>
+          <t>2932; 14269</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>968; 8511</t>
+          <t>957; 9221</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6144</t>
+          <t>0; 6022</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6464</t>
+          <t>0; 7468</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4772</t>
+          <t>0; 3924</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5244</t>
+          <t>0; 5238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 4932</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1025; 10632</t>
+          <t>1049; 9547</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1037; 8304</t>
+          <t>1031; 8283</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>969; 8412</t>
+          <t>964; 8234</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1983; 11310</t>
+          <t>1959; 10402</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5084</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4810</t>
+          <t>0; 4427</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 5118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 5695</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2101; 11252</t>
+          <t>2121; 11011</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1230; 10326</t>
+          <t>1228; 10247</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6173</t>
+          <t>0; 6207</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2942; 13399</t>
+          <t>3089; 12963</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1582; 11743</t>
+          <t>2039; 11784</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5347; 19648</t>
+          <t>5776; 21178</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9537; 27679</t>
+          <t>9748; 28174</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10492; 28417</t>
+          <t>11538; 27798</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10421; 28616</t>
+          <t>9967; 28037</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19166; 41051</t>
+          <t>19027; 41013</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14456; 34645</t>
+          <t>13903; 33511</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18906; 41571</t>
+          <t>19499; 43188</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>32835; 61688</t>
+          <t>32198; 61828</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30033; 55725</t>
+          <t>28981; 54461</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
